--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0002T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>85.96682528594592</v>
+        <v>13.96960910896621</v>
       </c>
       <c r="D2" t="n">
-        <v>1.368199367852013</v>
+        <v>0.2223323972759521</v>
       </c>
       <c r="E2" t="n">
-        <v>40.11932986177259</v>
+        <v>6.519391102538047</v>
       </c>
       <c r="F2" t="n">
-        <v>19.22490825651694</v>
+        <v>3.124047591684002</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.728165562400727</v>
+        <v>0.9308269038901181</v>
       </c>
       <c r="D3" t="n">
-        <v>39.81801588088589</v>
+        <v>6.470427580643957</v>
       </c>
       <c r="E3" t="n">
-        <v>40.11932986177259</v>
+        <v>6.519391102538047</v>
       </c>
       <c r="F3" t="n">
-        <v>19.22490825651694</v>
+        <v>3.124047591684002</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
